--- a/output/laminas_comunales/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>1377104.12</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>1178531.88</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>1134129.12</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>1088746.12</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>1080293.5</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>1069051.75</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>1068515.5</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>1067164.62</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>1064567.5</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>1039362.56</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>1023269.94</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>1018240.94</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>998897.0600000001</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>996642.38</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>974855.1899999999</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>956830.3100000001</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>940958.1899999999</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>931260.62</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>925215.88</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>921826.4399999999</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>911898.8100000001</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>907957.1899999999</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>906019.6899999999</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>892445.5</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>888797.1899999999</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>888642.8100000001</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>887823.4399999999</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>887522.9399999999</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>880259.75</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>864130.38</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>851294.3100000001</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>830449.25</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -812,9 +711,6 @@
       <c r="B34">
         <v>829019.62</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -825,9 +721,6 @@
       <c r="B35">
         <v>821303.1899999999</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -838,9 +731,6 @@
       <c r="B36">
         <v>820204.12</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -851,9 +741,6 @@
       <c r="B37">
         <v>818072.9399999999</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -864,9 +751,6 @@
       <c r="B38">
         <v>813232.88</v>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -876,9 +760,6 @@
       </c>
       <c r="B39">
         <v>782835.75</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>1377104.12</v>
       </c>
+      <c r="C2">
+        <v>1213778.5</v>
+      </c>
+      <c r="D2">
+        <v>163325.6200000001</v>
+      </c>
+      <c r="E2">
+        <v>13.45596581254325</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>1178531.88</v>
       </c>
+      <c r="C3">
+        <v>1047217.81</v>
+      </c>
+      <c r="D3">
+        <v>131314.0699999998</v>
+      </c>
+      <c r="E3">
+        <v>12.53932742033865</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>1134129.12</v>
       </c>
+      <c r="C4">
+        <v>991712.88</v>
+      </c>
+      <c r="D4">
+        <v>142416.2400000001</v>
+      </c>
+      <c r="E4">
+        <v>14.36063228300515</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>1088746.12</v>
       </c>
+      <c r="C5">
+        <v>964421.9399999999</v>
+      </c>
+      <c r="D5">
+        <v>124324.1800000002</v>
+      </c>
+      <c r="E5">
+        <v>12.89105679200955</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>1080293.5</v>
       </c>
+      <c r="C6">
+        <v>924962.75</v>
+      </c>
+      <c r="D6">
+        <v>155330.75</v>
+      </c>
+      <c r="E6">
+        <v>16.79318977980464</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>1069051.75</v>
       </c>
+      <c r="C7">
+        <v>877058</v>
+      </c>
+      <c r="D7">
+        <v>191993.75</v>
+      </c>
+      <c r="E7">
+        <v>21.89065603415052</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>1068515.5</v>
       </c>
+      <c r="C8">
+        <v>875038.1899999999</v>
+      </c>
+      <c r="D8">
+        <v>193477.3100000001</v>
+      </c>
+      <c r="E8">
+        <v>22.11072753293202</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>1067164.62</v>
       </c>
+      <c r="C9">
+        <v>757737.1899999999</v>
+      </c>
+      <c r="D9">
+        <v>309427.4300000002</v>
+      </c>
+      <c r="E9">
+        <v>40.83571904396037</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>1064567.5</v>
       </c>
+      <c r="C10">
+        <v>954175.6899999999</v>
+      </c>
+      <c r="D10">
+        <v>110391.8100000001</v>
+      </c>
+      <c r="E10">
+        <v>11.56933792769339</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>1039362.56</v>
       </c>
+      <c r="C11">
+        <v>904273.3100000001</v>
+      </c>
+      <c r="D11">
+        <v>135089.25</v>
+      </c>
+      <c r="E11">
+        <v>14.93898454218447</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,6 +581,15 @@
       <c r="B12">
         <v>1023269.94</v>
       </c>
+      <c r="C12">
+        <v>922088.0600000001</v>
+      </c>
+      <c r="D12">
+        <v>101181.8799999999</v>
+      </c>
+      <c r="E12">
+        <v>10.97312549519403</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +600,15 @@
       <c r="B13">
         <v>1018240.94</v>
       </c>
+      <c r="C13">
+        <v>895670.8100000001</v>
+      </c>
+      <c r="D13">
+        <v>122570.1299999999</v>
+      </c>
+      <c r="E13">
+        <v>13.68472977253774</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +619,15 @@
       <c r="B14">
         <v>998897.0600000001</v>
       </c>
+      <c r="C14">
+        <v>863580.0600000001</v>
+      </c>
+      <c r="D14">
+        <v>135317</v>
+      </c>
+      <c r="E14">
+        <v>15.66930575029719</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,245 +638,471 @@
       <c r="B15">
         <v>996642.38</v>
       </c>
+      <c r="C15">
+        <v>893030.8100000001</v>
+      </c>
+      <c r="D15">
+        <v>103611.5699999999</v>
+      </c>
+      <c r="E15">
+        <v>11.60223912095484</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Juan Fernandez</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B16">
-        <v>974855.1899999999</v>
+        <v>985180.3100000001</v>
+      </c>
+      <c r="C16">
+        <v>871590.12</v>
+      </c>
+      <c r="D16">
+        <v>113590.1900000001</v>
+      </c>
+      <c r="E16">
+        <v>13.03252381979732</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="B17">
-        <v>956830.3100000001</v>
+        <v>974855.1899999999</v>
+      </c>
+      <c r="C17">
+        <v>862059.88</v>
+      </c>
+      <c r="D17">
+        <v>112795.3099999999</v>
+      </c>
+      <c r="E17">
+        <v>13.08439385904374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="B18">
-        <v>940958.1899999999</v>
+        <v>956830.3100000001</v>
+      </c>
+      <c r="C18">
+        <v>838004.12</v>
+      </c>
+      <c r="D18">
+        <v>118826.1900000001</v>
+      </c>
+      <c r="E18">
+        <v>14.17966656297585</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B19">
-        <v>931260.62</v>
+        <v>940958.1899999999</v>
+      </c>
+      <c r="C19">
+        <v>841343.5600000001</v>
+      </c>
+      <c r="D19">
+        <v>99614.62999999989</v>
+      </c>
+      <c r="E19">
+        <v>11.83994681078915</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B20">
-        <v>925215.88</v>
+        <v>931260.62</v>
+      </c>
+      <c r="C20">
+        <v>821232.62</v>
+      </c>
+      <c r="D20">
+        <v>110028</v>
+      </c>
+      <c r="E20">
+        <v>13.397909108871</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="B21">
-        <v>921826.4399999999</v>
+        <v>925215.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="B22">
-        <v>911898.8100000001</v>
+        <v>921826.4399999999</v>
+      </c>
+      <c r="C22">
+        <v>777892.25</v>
+      </c>
+      <c r="D22">
+        <v>143934.1899999999</v>
+      </c>
+      <c r="E22">
+        <v>18.50310116857443</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B23">
-        <v>907957.1899999999</v>
+        <v>911898.8100000001</v>
+      </c>
+      <c r="C23">
+        <v>802994.1899999999</v>
+      </c>
+      <c r="D23">
+        <v>108904.6200000001</v>
+      </c>
+      <c r="E23">
+        <v>13.56231730643034</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="B24">
-        <v>906019.6899999999</v>
+        <v>907957.1899999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B25">
-        <v>892445.5</v>
+        <v>906019.6899999999</v>
+      </c>
+      <c r="C25">
+        <v>775798.75</v>
+      </c>
+      <c r="D25">
+        <v>130220.9399999999</v>
+      </c>
+      <c r="E25">
+        <v>16.78540214198592</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="B26">
-        <v>888797.1899999999</v>
+        <v>892445.5</v>
+      </c>
+      <c r="C26">
+        <v>775832.5</v>
+      </c>
+      <c r="D26">
+        <v>116613</v>
+      </c>
+      <c r="E26">
+        <v>15.03069283640477</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="B27">
-        <v>888642.8100000001</v>
+        <v>888797.1899999999</v>
+      </c>
+      <c r="C27">
+        <v>795889.4399999999</v>
+      </c>
+      <c r="D27">
+        <v>92907.75</v>
+      </c>
+      <c r="E27">
+        <v>11.67344926702383</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="B28">
-        <v>887823.4399999999</v>
+        <v>888642.8100000001</v>
+      </c>
+      <c r="C28">
+        <v>749486</v>
+      </c>
+      <c r="D28">
+        <v>139156.8100000001</v>
+      </c>
+      <c r="E28">
+        <v>18.56696589395934</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="B29">
-        <v>887522.9399999999</v>
+        <v>887823.4399999999</v>
+      </c>
+      <c r="C29">
+        <v>774882.88</v>
+      </c>
+      <c r="D29">
+        <v>112940.5599999999</v>
+      </c>
+      <c r="E29">
+        <v>14.57517812240219</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="B30">
-        <v>880259.75</v>
+        <v>887522.9399999999</v>
+      </c>
+      <c r="C30">
+        <v>780874</v>
+      </c>
+      <c r="D30">
+        <v>106648.9399999999</v>
+      </c>
+      <c r="E30">
+        <v>13.65763746776048</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B31">
-        <v>864130.38</v>
+        <v>880259.75</v>
+      </c>
+      <c r="C31">
+        <v>780163.88</v>
+      </c>
+      <c r="D31">
+        <v>100095.87</v>
+      </c>
+      <c r="E31">
+        <v>12.83010820752173</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="B32">
-        <v>851294.3100000001</v>
+        <v>864130.38</v>
+      </c>
+      <c r="C32">
+        <v>724756.75</v>
+      </c>
+      <c r="D32">
+        <v>139373.63</v>
+      </c>
+      <c r="E32">
+        <v>19.2304010966438</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="B33">
-        <v>830449.25</v>
+        <v>851294.3100000001</v>
+      </c>
+      <c r="C33">
+        <v>740788.9399999999</v>
+      </c>
+      <c r="D33">
+        <v>110505.3700000001</v>
+      </c>
+      <c r="E33">
+        <v>14.91725429918003</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="B34">
-        <v>829019.62</v>
+        <v>830449.25</v>
+      </c>
+      <c r="C34">
+        <v>736834.88</v>
+      </c>
+      <c r="D34">
+        <v>93614.37</v>
+      </c>
+      <c r="E34">
+        <v>12.70493193807547</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B35">
-        <v>821303.1899999999</v>
+        <v>829019.62</v>
+      </c>
+      <c r="C35">
+        <v>717598.62</v>
+      </c>
+      <c r="D35">
+        <v>111421</v>
+      </c>
+      <c r="E35">
+        <v>15.52692506571431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="B36">
-        <v>820204.12</v>
+        <v>821303.1899999999</v>
+      </c>
+      <c r="C36">
+        <v>720734.62</v>
+      </c>
+      <c r="D36">
+        <v>100568.5699999999</v>
+      </c>
+      <c r="E36">
+        <v>13.95361998845011</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="B37">
-        <v>818072.9399999999</v>
+        <v>820204.12</v>
+      </c>
+      <c r="C37">
+        <v>708746.6899999999</v>
+      </c>
+      <c r="D37">
+        <v>111457.4300000001</v>
+      </c>
+      <c r="E37">
+        <v>15.72598949280455</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="B38">
-        <v>813232.88</v>
+        <v>818072.9399999999</v>
+      </c>
+      <c r="C38">
+        <v>703407.75</v>
+      </c>
+      <c r="D38">
+        <v>114665.1899999999</v>
+      </c>
+      <c r="E38">
+        <v>16.30138280392843</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Santa María</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>813232.88</v>
+      </c>
+      <c r="C39">
+        <v>706345</v>
+      </c>
+      <c r="D39">
+        <v>106887.88</v>
+      </c>
+      <c r="E39">
+        <v>15.13253155327778</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Cartagena</t>
         </is>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>782835.75</v>
+      </c>
+      <c r="C40">
+        <v>694493.12</v>
+      </c>
+      <c r="D40">
+        <v>88342.63</v>
+      </c>
+      <c r="E40">
+        <v>12.72044710824494</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -1112,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1121,20 +1121,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1068515.5</v>
+          <t>Rinconada</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1143,48 +1135,33 @@
           <t>Cabildo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>892445.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>907957.1899999999</v>
+          <t>Petorca</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1018240.94</v>
+          <t>Panquehue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>782835.75</v>
+          <t>Olmué</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>906019.6899999999</v>
+          <t>Cartagena</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1193,148 +1170,103 @@
           <t>Catemu</t>
         </is>
       </c>
-      <c r="B8">
-        <v>887522.9399999999</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1377104.12</v>
+          <t>Llaillay</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>820204.12</v>
+          <t>San Felipe</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>888797.1899999999</v>
+          <t>Santa María</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>851294.3100000001</v>
+          <t>Villa Alemana</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>1178531.88</v>
+          <t>Santo Domingo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>830449.25</v>
+          <t>San Antonio</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>887823.4399999999</v>
+          <t>El Tabo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>925215.88</v>
+          <t>El Quisco</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>1088746.12</v>
+          <t>Algarrobo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>998897.0600000001</v>
+          <t>Casablanca</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>864130.38</v>
+          <t>Valparaíso</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>818072.9399999999</v>
+          <t>Viña del Mar</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>888642.8100000001</v>
+          <t>Concón</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>829019.62</v>
+          <t>Quintero</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1343,148 +1275,103 @@
           <t>Puchuncaví</t>
         </is>
       </c>
-      <c r="B23">
-        <v>921826.4399999999</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>821303.1899999999</v>
+          <t>Zapallar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>931260.62</v>
+          <t>Papudo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>1023269.94</v>
+          <t>La Ligua</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>956830.3100000001</v>
+          <t>Limache</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>1080293.5</v>
+          <t>Quillota</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>880259.75</v>
+          <t>Calera</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>1039362.56</v>
+          <t>Nogales</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>911898.8100000001</v>
+          <t>Calle Larga</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>813232.88</v>
+          <t>La Cruz</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>1134129.12</v>
+          <t>Putaendo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>940958.1899999999</v>
+          <t>San Esteban</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>996642.38</v>
+          <t>Los Andes</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>1064567.5</v>
+          <t>Hijuelas</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>1067164.62</v>
+          <t>Quilpué</t>
+        </is>
       </c>
     </row>
   </sheetData>
